--- a/SubClase/UOri_SubClase.xlsx
+++ b/SubClase/UOri_SubClase.xlsx
@@ -680,13 +680,13 @@
         <v>1.299483507745535</v>
       </c>
       <c r="C2" s="2">
-        <v>108.3158827229102</v>
+        <v>107.9829060410318</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.407547032253214</v>
+        <v>1.403220055187566</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1077,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="2">
-        <v>3.260334690503112</v>
+        <v>3.260334690503114</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="E32" s="2">
-        <v>1.486125307298083</v>
+        <v>1.486125307298084</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1221,7 +1221,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>3.859857761799671</v>
+        <v>3.85985776179967</v>
       </c>
       <c r="C34" s="2">
         <v>129.0491344788341</v>
@@ -1374,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="B43" s="2">
-        <v>0.8586952689806903</v>
+        <v>0.8586952689806904</v>
       </c>
       <c r="C43" s="2">
         <v>110.5739135972713</v>
@@ -1383,7 +1383,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="2">
-        <v>0.9494929647865646</v>
+        <v>0.9494929647865648</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1935,7 +1935,7 @@
         <v>80</v>
       </c>
       <c r="B76" s="2">
-        <v>1.953489668068934</v>
+        <v>1.953489668068935</v>
       </c>
       <c r="C76" s="2">
         <v>113.378498566931</v>
@@ -1952,7 +1952,7 @@
         <v>81</v>
       </c>
       <c r="B77" s="2">
-        <v>2.311038222617364</v>
+        <v>2.311038222617363</v>
       </c>
       <c r="C77" s="2">
         <v>143.8214267455496</v>
